--- a/diseases/d058/2026-2029.xlsx
+++ b/diseases/d058/2026-2029.xlsx
@@ -439,110 +439,255 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>record_kind</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>country_code</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>country_name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>disease_id</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>disease_name_en</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>disease_name_zh</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>year_month</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>cases</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>weekly_equiv_cases</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>deaths</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>incidence_rate_per_100k</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>incidence_rate_source</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>mortality_rate</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>series_code</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>source_series_code</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>source_system</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>source_label</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>metric_type</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>reporting_basis</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>temporal_granularity</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>geography_key</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>dimension_key</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>mapping_relation</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>comparability</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>aggregation_policy</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>availability_status</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>missing_value_policy</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>definition_version</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>case_definition</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>case_definition_uri</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>quality_status</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>is_selected_series</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>data_layer</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>projection_policy</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>coverage_status</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>loss_risk</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>selected_series_codes</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>available_series_count</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>provenance_note</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
         <is>
           <t>primary_source_scope</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>primary_source_label</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>primary_source_url</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>primary_source_type</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>source_scopes</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>source_labels</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>source_urls</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source_types</t>
         </is>
@@ -571,97 +716,126 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -690,97 +864,126 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>14</v>
       </c>
-      <c r="N3" t="n">
-        <v>3.161290322580645</v>
-      </c>
       <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
         <v>0.02713157893308864</v>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -809,97 +1012,126 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>TW</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Taiwan, China</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>22</v>
       </c>
-      <c r="N4" t="n">
-        <v>4.967741935483871</v>
-      </c>
       <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
         <v>0.09560523382161172</v>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -928,97 +1160,126 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>2026-01-10</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" t="n">
-        <v>1.5</v>
-      </c>
       <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
         <v>0.002450425222697299</v>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -1047,97 +1308,126 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
-      </c>
-      <c r="M6" t="n">
-        <v>7</v>
       </c>
       <c r="N6" t="n">
         <v>7</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
         <v>0.005717658852960364</v>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -1166,97 +1456,126 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
-      </c>
-      <c r="M7" t="n">
-        <v>8</v>
       </c>
       <c r="N7" t="n">
         <v>8</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
         <v>0.00653446726052613</v>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -1285,97 +1604,126 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
-      </c>
-      <c r="M8" t="n">
-        <v>4</v>
       </c>
       <c r="N8" t="n">
         <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
         <v>0.003267233630263065</v>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -1404,97 +1752,126 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AY9" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="BC9" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1523,97 +1900,126 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" t="n">
-        <v>0.9032258064516129</v>
-      </c>
       <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
         <v>0.007751879695168184</v>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="BC10" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -1642,97 +2048,126 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>TW</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Taiwan, China</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>4</v>
       </c>
-      <c r="N11" t="n">
-        <v>0.9032258064516129</v>
-      </c>
       <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>0.01738276978574758</v>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="AY11" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1761,97 +2196,126 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
-      </c>
-      <c r="M12" t="n">
-        <v>3</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
         <v>0.002450425222697299</v>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="AY12" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="BC12" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -1880,97 +2344,126 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
-      </c>
-      <c r="M13" t="n">
-        <v>2</v>
       </c>
       <c r="N13" t="n">
         <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>0.001633616815131532</v>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="AW13" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="AY13" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="BA13" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="BB13" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="BC13" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -1999,97 +2492,126 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
         <v>0.0008168084075657662</v>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="AW14" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="AY14" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="BA14" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="BB14" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="BC14" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -2118,97 +2640,126 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
         <v>0.0008168084075657662</v>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="AW15" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="AY15" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="BA15" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="BB15" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="BC15" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -2237,97 +2788,126 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="AW16" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="AY16" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="BA16" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="BB16" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="BC16" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -2356,97 +2936,126 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>7</v>
       </c>
-      <c r="N17" t="n">
-        <v>1.75</v>
-      </c>
       <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
         <v>0.01356578946654432</v>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="AW17" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="AY17" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="AZ17" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="BA17" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="BB17" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="BC17" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -2475,97 +3084,126 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>TW</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Taiwan, China</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>3</v>
       </c>
-      <c r="N18" t="n">
-        <v>0.75</v>
-      </c>
       <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
         <v>0.01303707733931069</v>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="AW18" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="AY18" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="BA18" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="BB18" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="BC18" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -2594,97 +3232,126 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="AW19" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="AY19" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="AZ19" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="BA19" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="BB19" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="BC19" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -2713,97 +3380,126 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="AW20" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="AY20" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="BA20" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="BB20" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="BC20" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -2832,97 +3528,126 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="AW21" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="AY21" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="AZ21" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="BA21" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="BB21" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="BC21" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -2951,97 +3676,126 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>2026-03-28</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
         <v>0.0008168084075657662</v>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="AW22" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="AX22" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="AY22" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="AZ22" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="BA22" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="BB22" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="BC22" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -3070,97 +3824,126 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="AW23" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="AX23" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="AY23" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="AZ23" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="BA23" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="BB23" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="BC23" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -3189,97 +3972,126 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>14</v>
       </c>
-      <c r="N24" t="n">
-        <v>3.161290322580645</v>
-      </c>
       <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
         <v>0.02713157893308864</v>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="AW24" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="AX24" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="AY24" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="AZ24" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="BA24" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="BB24" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="BC24" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -3308,97 +4120,126 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>TW</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Taiwan, China</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>15</v>
       </c>
-      <c r="N25" t="n">
-        <v>3.387096774193548</v>
-      </c>
       <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
         <v>0.06518538669655344</v>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="AW25" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="AY25" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="BA25" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="BB25" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="BC25" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -3427,97 +4268,126 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>2026-04-04</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="AW26" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="AX26" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="AY26" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="AZ26" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="BA26" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="BB26" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="BC26" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -3546,97 +4416,126 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="AW27" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="AX27" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="AY27" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="AZ27" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="BA27" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="BB27" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="BC27" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -3665,97 +4564,126 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
-      </c>
-      <c r="M28" t="n">
-        <v>1</v>
       </c>
       <c r="N28" t="n">
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
         <v>0.0008168084075657662</v>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="AW28" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="AX28" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="AY28" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="AZ28" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="BA28" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="BB28" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="BC28" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -3784,97 +4712,126 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>2026-04-25</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
-      </c>
-      <c r="M29" t="n">
-        <v>1</v>
       </c>
       <c r="N29" t="n">
         <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
         <v>0.0008168084075657662</v>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="AW29" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="AX29" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="AY29" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="AZ29" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="BA29" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="BB29" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="BC29" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -3903,97 +4860,126 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>2</v>
       </c>
-      <c r="N30" t="n">
-        <v>0.4666666666666667</v>
-      </c>
       <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
         <v>0.02710540560393419</v>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="AW30" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="AX30" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="AY30" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="AZ30" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="BA30" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="BB30" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="BC30" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -4022,97 +5008,126 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>19</v>
       </c>
-      <c r="N31" t="n">
-        <v>4.433333333333334</v>
-      </c>
       <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
         <v>0.03682142855204888</v>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="AW31" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="AX31" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="AY31" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="AZ31" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="BA31" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="BB31" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="BC31" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -4141,97 +5156,126 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>TW</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Taiwan, China</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>43</v>
       </c>
-      <c r="N32" t="n">
-        <v>10.03333333333333</v>
-      </c>
       <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
         <v>0.1868647751967865</v>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="AW32" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="AX32" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="AY32" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="AZ32" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="BA32" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="BB32" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="BC32" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -4260,97 +5304,126 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
-      </c>
-      <c r="M33" t="n">
-        <v>3</v>
       </c>
       <c r="N33" t="n">
         <v>3</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
         <v>0.002450425222697299</v>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="AW33" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="AX33" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="AY33" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="AZ33" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="BA33" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="BB33" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="BC33" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -4379,97 +5452,126 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
-      </c>
-      <c r="M34" t="n">
-        <v>2</v>
       </c>
       <c r="N34" t="n">
         <v>2</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
         <v>0.001633616815131532</v>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="AW34" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="AX34" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="AY34" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="AZ34" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="BA34" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="BB34" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="BC34" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -4498,97 +5600,126 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
-      </c>
-      <c r="M35" t="n">
-        <v>2</v>
       </c>
       <c r="N35" t="n">
         <v>2</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
         <v>0.001633616815131532</v>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="AW35" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="AX35" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="AY35" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="AZ35" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="BA35" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="BB35" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="BC35" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -4617,97 +5748,126 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
-      </c>
-      <c r="M36" t="n">
-        <v>3</v>
       </c>
       <c r="N36" t="n">
         <v>3</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
         <v>0.002450425222697299</v>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="AW36" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="AX36" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="AY36" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="AZ36" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="BA36" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="BB36" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="BC36" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -4736,97 +5896,126 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
-      </c>
-      <c r="M37" t="n">
-        <v>2</v>
       </c>
       <c r="N37" t="n">
         <v>2</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
         <v>0.001633616815131532</v>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="AW37" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="AX37" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="AY37" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="AZ37" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="BA37" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="BB37" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
+      <c r="BC37" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -4855,97 +6044,126 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>3</v>
       </c>
-      <c r="N38" t="n">
-        <v>0.6774193548387096</v>
-      </c>
       <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
         <v>0.04065810840590128</v>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="AW38" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="AX38" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="AY38" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="AZ38" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="BA38" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="BB38" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
+      <c r="BC38" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -4974,97 +6192,126 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>28</v>
       </c>
-      <c r="N39" t="n">
-        <v>6.32258064516129</v>
-      </c>
       <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
         <v>0.05426315786617728</v>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="AW39" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="AX39" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="AY39" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="AZ39" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="BA39" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="BB39" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="BC39" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -5093,97 +6340,126 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>TW</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>Taiwan, China</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>28</v>
       </c>
-      <c r="N40" t="n">
-        <v>6.32258064516129</v>
-      </c>
       <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
         <v>0.1216793885002331</v>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV40" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="AW40" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="AX40" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="AY40" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="AZ40" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="BA40" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="BB40" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="BC40" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -5212,97 +6488,126 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
-      </c>
-      <c r="M41" t="n">
-        <v>4</v>
       </c>
       <c r="N41" t="n">
         <v>4</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
         <v>0.003267233630263065</v>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV41" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="AW41" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="AX41" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="AY41" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="AZ41" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="BA41" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="BB41" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="BC41" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -5331,97 +6636,126 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
-      </c>
-      <c r="M42" t="n">
-        <v>2</v>
       </c>
       <c r="N42" t="n">
         <v>2</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
         <v>0.001633616815131532</v>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV42" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="AW42" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="AX42" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="AY42" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="AZ42" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="BA42" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="BB42" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="BC42" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -5450,97 +6784,126 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
-      </c>
-      <c r="M43" t="n">
-        <v>1</v>
       </c>
       <c r="N43" t="n">
         <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
         <v>0.0008168084075657662</v>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV43" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="AW43" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="AX43" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="AY43" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="AZ43" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="BA43" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="BB43" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="BC43" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -5569,97 +6932,126 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
-      </c>
-      <c r="M44" t="n">
-        <v>1</v>
       </c>
       <c r="N44" t="n">
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
         <v>0.0008168084075657662</v>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="AW44" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="AX44" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="AY44" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="AZ44" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="BA44" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="BB44" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="BC44" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -5688,97 +7080,126 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>18</v>
       </c>
-      <c r="N45" t="n">
-        <v>4.2</v>
-      </c>
       <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
         <v>0.03488345862825683</v>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="AW45" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="AX45" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="AY45" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="AZ45" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="BA45" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="BB45" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="BC45" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -5807,97 +7228,126 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>TW</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Taiwan, China</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="M46" t="n">
-        <v>17</v>
-      </c>
       <c r="N46" t="n">
-        <v>3.966666666666667</v>
+        <v>20</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0.07387677158942724</v>
-      </c>
-      <c r="Q46" t="inlineStr">
+        <v>20</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.08691384892873792</v>
+      </c>
+      <c r="S46" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="AW46" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="AX46" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="AY46" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="AZ46" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="BA46" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="BB46" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="BC46" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -5926,97 +7376,126 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>2026-07-04</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
-      </c>
-      <c r="M47" t="n">
-        <v>2</v>
       </c>
       <c r="N47" t="n">
         <v>2</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
         <v>0.001633616815131532</v>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="AW47" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="AX47" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="AY47" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="AZ47" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="BA47" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="BB47" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
+      <c r="BC47" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -6045,97 +7524,126 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="inlineStr">
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV48" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="AW48" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="AX48" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="AY48" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="AZ48" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="BA48" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="BB48" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
+      <c r="BC48" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -6164,97 +7672,126 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
-      </c>
-      <c r="M49" t="n">
-        <v>2</v>
       </c>
       <c r="N49" t="n">
         <v>2</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
         <v>0.001633616815131532</v>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="AW49" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="AX49" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="AY49" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="AZ49" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="BA49" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="BB49" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="BC49" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -6283,97 +7820,126 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
       <c r="N50" t="n">
         <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="inlineStr">
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="AW50" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="AX50" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="AY50" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="AZ50" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="BA50" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="BB50" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="BC50" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -6402,97 +7968,126 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
       <c r="N51" t="n">
         <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="inlineStr">
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV51" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="AW51" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="AX51" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="AY51" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="AZ51" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="BA51" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="BB51" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="BC51" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -6521,99 +8116,276 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>D058</t>
-        </is>
-      </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
           <t>恙虫病</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="M52" t="n">
-        <v>1</v>
-      </c>
       <c r="N52" t="n">
-        <v>0.2258064516129032</v>
+        <v>2</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0.001937969923792046</v>
-      </c>
-      <c r="Q52" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.003875939847584092</v>
+      </c>
+      <c r="S52" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="AW52" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="AX52" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="AY52" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="AZ52" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="BA52" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="BB52" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
+      <c r="BC52" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>scrub-typhus</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>恙虫病</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>2</v>
+      </c>
+      <c r="O53" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0.008691384892873792</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -6729,37 +8501,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>record_count</t>
+          <t>projection_record_count</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>schema_version</t>
+          <t>record_count</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>total_cases</t>
+          <t>schema_version</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>298</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>total_deaths</t>
+          <t>source_observation_count</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -6769,22 +8541,64 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>window_end</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2029-12-31</t>
-        </is>
+          <t>source_series_count</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>total_basis</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>total_cases</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>total_deaths</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2029-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>window_start</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>

--- a/diseases/d058/2026-2029.xlsx
+++ b/diseases/d058/2026-2029.xlsx
@@ -7272,16 +7272,16 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O46" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.08691384892873792</v>
+        <v>0.09125954137517482</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d058/2026-2029.xlsx
+++ b/diseases/d058/2026-2029.xlsx
@@ -8160,16 +8160,16 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.009689849618960231</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d058/2026-2029.xlsx
+++ b/diseases/d058/2026-2029.xlsx
@@ -7272,16 +7272,16 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O46" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.09125954137517482</v>
+        <v>0.09560523382161172</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -8386,6 +8386,154 @@
       <c r="BC53" t="inlineStr">
         <is>
           <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>scrub-typhus</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>恙虫病</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr"/>
+      <c r="AT54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8422,7 +8570,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -8505,7 +8653,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -8515,7 +8663,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11">
@@ -8567,7 +8715,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d058/2026-2029.xlsx
+++ b/diseases/d058/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -913,9 +910,6 @@
       <c r="O3" t="n">
         <v>14</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.02713157893308864</v>
       </c>
@@ -1801,9 +1795,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -1949,9 +1940,6 @@
       <c r="O10" t="n">
         <v>4</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.007751879695168184</v>
       </c>
@@ -2837,9 +2825,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -2985,9 +2970,6 @@
       <c r="O17" t="n">
         <v>7</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.01356578946654432</v>
       </c>
@@ -3873,9 +3855,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4021,9 +4000,6 @@
       <c r="O24" t="n">
         <v>14</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.02713157893308864</v>
       </c>
@@ -4169,9 +4145,6 @@
       <c r="O25" t="n">
         <v>15</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.06518538669655344</v>
       </c>
@@ -4909,9 +4882,6 @@
       <c r="O30" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -5057,9 +5027,6 @@
       <c r="O31" t="n">
         <v>19</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.03682142855204888</v>
       </c>
@@ -5205,9 +5172,6 @@
       <c r="O32" t="n">
         <v>43</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.1868647751967865</v>
       </c>
@@ -6093,9 +6057,6 @@
       <c r="O38" t="n">
         <v>3</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.04065810840590128</v>
       </c>
@@ -6241,9 +6202,6 @@
       <c r="O39" t="n">
         <v>28</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.05426315786617728</v>
       </c>
@@ -6389,9 +6347,6 @@
       <c r="O40" t="n">
         <v>28</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.1216793885002331</v>
       </c>
@@ -6537,9 +6492,6 @@
       <c r="O41" t="n">
         <v>4</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.003267233630263065</v>
       </c>
@@ -6685,9 +6637,6 @@
       <c r="O42" t="n">
         <v>2</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -6833,9 +6782,6 @@
       <c r="O43" t="n">
         <v>1</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -6981,9 +6927,6 @@
       <c r="O44" t="n">
         <v>1</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -7129,9 +7072,6 @@
       <c r="O45" t="n">
         <v>18</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.03488345862825683</v>
       </c>
@@ -7277,9 +7217,6 @@
       <c r="O46" t="n">
         <v>22</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.09560523382161172</v>
       </c>
@@ -7425,9 +7362,6 @@
       <c r="O47" t="n">
         <v>2</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -7573,9 +7507,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -7721,9 +7652,6 @@
       <c r="O49" t="n">
         <v>2</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -7869,9 +7797,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -8017,9 +7942,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -8165,9 +8087,6 @@
       <c r="O52" t="n">
         <v>5</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.009689849618960231</v>
       </c>
@@ -8308,16 +8227,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O53" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R53" t="n">
-        <v>0.008691384892873792</v>
+        <v>0.01738276978574758</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -8459,9 +8375,6 @@
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
@@ -8715,7 +8628,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d058/2026-2029.xlsx
+++ b/diseases/d058/2026-2029.xlsx
@@ -8082,13 +8082,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R52" t="n">
-        <v>0.009689849618960231</v>
+        <v>0.01162781954275227</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d058/2026-2029.xlsx
+++ b/diseases/d058/2026-2029.xlsx
@@ -8227,13 +8227,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R53" t="n">
-        <v>0.01738276978574758</v>
+        <v>0.02172846223218448</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d058/2026-2029.xlsx
+++ b/diseases/d058/2026-2029.xlsx
@@ -8450,6 +8450,151 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>scrub-typhus</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>恙虫病</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8483,7 +8628,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -8566,7 +8711,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
@@ -8576,7 +8721,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d058/2026-2029.xlsx
+++ b/diseases/d058/2026-2029.xlsx
@@ -7067,13 +7067,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O45" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R45" t="n">
-        <v>0.03488345862825683</v>
+        <v>0.03682142855204888</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -8082,13 +8082,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O52" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R52" t="n">
-        <v>0.01162781954275227</v>
+        <v>0.01937969923792046</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -8590,6 +8590,151 @@
         </is>
       </c>
       <c r="BC55" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>scrub-typhus</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>恙虫病</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA56" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC56" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -8628,7 +8773,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8856,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">
@@ -8721,7 +8866,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
@@ -8773,7 +8918,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d058/2026-2029.xlsx
+++ b/diseases/d058/2026-2029.xlsx
@@ -6052,13 +6052,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R38" t="n">
-        <v>0.04065810840590128</v>
+        <v>0.05421081120786837</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -7028,12 +7028,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7067,13 +7067,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>0.03682142855204888</v>
+        <v>0.01355270280196709</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -7106,42 +7106,42 @@
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -7173,12 +7173,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7212,13 +7212,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="O46" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="R46" t="n">
-        <v>0.09560523382161172</v>
+        <v>0.03682142855204888</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -7251,42 +7251,42 @@
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -7318,12 +7318,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -7357,13 +7357,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="O47" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="R47" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.09560523382161172</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -7396,42 +7396,42 @@
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -7502,13 +7502,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -7647,13 +7647,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0.001633616815131532</v>
+        <v>0</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -7792,13 +7792,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -8043,12 +8043,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -8073,22 +8073,22 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>0.01937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -8121,42 +8121,42 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8188,12 +8188,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -8227,13 +8227,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O53" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="R53" t="n">
-        <v>0.02172846223218448</v>
+        <v>0.0251936090092966</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -8266,42 +8266,42 @@
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -8333,12 +8333,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -8363,7 +8363,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -8372,13 +8372,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>0.02172846223218448</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -8411,42 +8411,42 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8508,7 +8508,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -8735,6 +8735,151 @@
         </is>
       </c>
       <c r="BC56" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>scrub-typhus</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>恙虫病</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr"/>
+      <c r="AT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -8856,7 +9001,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10">
@@ -8866,7 +9011,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
@@ -8918,7 +9063,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d058/2026-2029.xlsx
+++ b/diseases/d058/2026-2029.xlsx
@@ -7212,13 +7212,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O46" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R46" t="n">
-        <v>0.03682142855204888</v>
+        <v>0.03875939847584092</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -8227,13 +8227,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O53" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="R53" t="n">
-        <v>0.0251936090092966</v>
+        <v>0.03100751878067274</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -8882,6 +8882,296 @@
       <c r="BC57" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>scrub-typhus</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>恙虫病</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr"/>
+      <c r="AT58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV58" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA58" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>scrub-typhus</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>恙虫病</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0.001937969923792046</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr"/>
+      <c r="AT59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV59" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA59" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -8918,7 +9208,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -9001,7 +9291,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10">
@@ -9011,7 +9301,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
@@ -9063,7 +9353,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="16">
